--- a/gamer_forms/032_game_contact_form--gamer_forms.xlsx
+++ b/gamer_forms/032_game_contact_form--gamer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tags</t>
+          <t>Tags2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tags</t>
+          <t>Tags3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tags</t>
+          <t>Tags4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Game Title</t>
+          <t>Game Title2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Game Description</t>
+          <t>Game Description2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Game Rating</t>
+          <t>Game Rating2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Game Genre</t>
+          <t>Game Genre2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Release Date</t>
+          <t>Release Date2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Play Time</t>
+          <t>Play Time2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Price2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Platform2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>tags3</t>
+          <t>tags3_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tags</t>
+          <t>Tags3 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>tags4</t>
+          <t>tags4_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tags</t>
+          <t>Tags4 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tags</t>
+          <t>Tags5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tags</t>
+          <t>Tags6</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tags</t>
+          <t>Tags7</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tags</t>
+          <t>Tags8</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tags</t>
+          <t>Tags9</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tags</t>
+          <t>Tags10</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1351,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1401,29 +1401,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>game_selection_choices</t>
+          <t>contact_selection_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1452,29 +1452,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>contact_selection_choices</t>
+          <t>game_title_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>maybe</t>
+          <t>game_a</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Game A</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>game_a</t>
+          <t>game_b</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Game A</t>
+          <t>Game B</t>
         </is>
       </c>
     </row>
@@ -1503,29 +1503,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>game_b</t>
+          <t>game_c</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Game B</t>
+          <t>Game C</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>game_title_choices</t>
+          <t>game_genre_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>game_c</t>
+          <t>action</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Game C</t>
+          <t>Action</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>action</t>
+          <t>adventure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Adventure</t>
         </is>
       </c>
     </row>
@@ -1554,29 +1554,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>adventure</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Adventure</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>game_genre_choices</t>
+          <t>platform_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>PC</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>console</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>Console</t>
         </is>
       </c>
     </row>
@@ -1605,29 +1605,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>console</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>platform_choices</t>
+          <t>tags_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mobile</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>tag_1</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tag 1</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
@@ -1656,29 +1656,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>tag_2</t>
+          <t>tag_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tag 2</t>
+          <t>Tag 3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tags_choices</t>
+          <t>tags2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>tag_3</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tag 3</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>tag_1</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tag 1</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
@@ -1707,29 +1707,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>tag_2</t>
+          <t>tag_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tag 2</t>
+          <t>Tag 3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tags2_choices</t>
+          <t>tags3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>tag_3</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tag 3</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
@@ -1741,12 +1741,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>tag_1</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tag 1</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
@@ -1758,29 +1758,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>tag_2</t>
+          <t>tag_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tag 2</t>
+          <t>Tag 3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tags3_choices</t>
+          <t>tags4_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>tag_3</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tag 3</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>tag_1</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tag 1</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
@@ -1809,29 +1809,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>tag_2</t>
+          <t>tag_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tag 2</t>
+          <t>Tag 3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tags4_choices</t>
+          <t>game_title2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>tag_3</t>
+          <t>game_a</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tag 3</t>
+          <t>Game A</t>
         </is>
       </c>
     </row>
@@ -1843,12 +1843,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>game_a</t>
+          <t>game_b</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Game A</t>
+          <t>Game B</t>
         </is>
       </c>
     </row>
@@ -1860,29 +1860,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>game_b</t>
+          <t>game_c</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Game B</t>
+          <t>Game C</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>game_title2_choices</t>
+          <t>game_genre2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>game_c</t>
+          <t>action</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Game C</t>
+          <t>Action</t>
         </is>
       </c>
     </row>
@@ -1894,12 +1894,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>action</t>
+          <t>adventure</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Adventure</t>
         </is>
       </c>
     </row>
@@ -1911,29 +1911,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>adventure</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Adventure</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>game_genre2_choices</t>
+          <t>platform2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>pc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>PC</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>pc</t>
+          <t>console</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>Console</t>
         </is>
       </c>
     </row>
@@ -1962,131 +1962,131 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>console</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>platform2_choices</t>
+          <t>tags3_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>mobile</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tags3_choices</t>
+          <t>tags3_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>tag_1</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tag 1</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>tags3_choices</t>
+          <t>tags3_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>tag_2</t>
+          <t>tag_3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tag 2</t>
+          <t>Tag 3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tags3_choices</t>
+          <t>tags4_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>tag_3</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tag 3</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>tags4_choices</t>
+          <t>tags4_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>tag_1</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tag 1</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tags4_choices</t>
+          <t>tags4_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>tag_2</t>
+          <t>tag_3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tag 2</t>
+          <t>Tag 3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>tags4_choices</t>
+          <t>tags5_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>tag_3</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tag 3</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>tag_1</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tag 1</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
@@ -2115,29 +2115,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>tag_2</t>
+          <t>tag_3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tag 2</t>
+          <t>Tag 3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>tags5_choices</t>
+          <t>tags6_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>tag_3</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tag 3</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>tag_1</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tag 1</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
@@ -2166,29 +2166,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>tag_2</t>
+          <t>tag_3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tag 2</t>
+          <t>Tag 3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>tags6_choices</t>
+          <t>tags7_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>tag_3</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tag 3</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>tag_1</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tag 1</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
@@ -2217,29 +2217,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>tag_2</t>
+          <t>tag_3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tag 2</t>
+          <t>Tag 3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>tags7_choices</t>
+          <t>tags8_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>tag_3</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tag 3</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
@@ -2251,12 +2251,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>tag_1</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tag 1</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
@@ -2268,29 +2268,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>tag_2</t>
+          <t>tag_3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tag 2</t>
+          <t>Tag 3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>tags8_choices</t>
+          <t>tags9_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>tag_3</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tag 3</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
@@ -2302,12 +2302,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>tag_1</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tag 1</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
@@ -2319,29 +2319,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>tag_2</t>
+          <t>tag_3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tag 2</t>
+          <t>Tag 3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>tags9_choices</t>
+          <t>tags10_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>tag_3</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tag 3</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>tag_1</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tag 1</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
@@ -2370,27 +2370,10 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>tag_2</t>
+          <t>tag_3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
-        <is>
-          <t>Tag 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>tags10_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>tag_3</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
         <is>
           <t>Tag 3</t>
         </is>
